--- a/Clinical_and_Mutational_Landscape/Data_clinical_info.xlsx
+++ b/Clinical_and_Mutational_Landscape/Data_clinical_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shanghaixia/Desktop/SP_project_Figure_code/Fig1_(B)_datasource_landscape/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shx/Desktop/SP_proje t_code_0422/Clinical_and_Mutational_Landscape/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B05E2E-230A-6842-A52F-1A566A8AC09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C277ABB3-0765-414E-9A7C-89CD6E129097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="500" windowWidth="28300" windowHeight="17440" xr2:uid="{907BA06D-21AE-FB4B-A741-DA2B74B97890}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{907BA06D-21AE-FB4B-A741-DA2B74B97890}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_clinical_info" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="126">
   <si>
     <t>P182545</t>
   </si>
@@ -330,15 +330,6 @@
     <t>NF1</t>
   </si>
   <si>
-    <t>Mut_Frameshift;CNV_Del</t>
-  </si>
-  <si>
-    <t>Mut_Stop_gain;CNV_Del</t>
-  </si>
-  <si>
-    <t>Mut_Missense;CNV_Del</t>
-  </si>
-  <si>
     <t>PDGFRA</t>
   </si>
   <si>
@@ -368,6 +359,70 @@
   </si>
   <si>
     <t>ID7</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Missense;CNV_Del</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Del</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Loss</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Gain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Missense;CNV_Loss</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Amp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Frameshift;CNV_Loss</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Stop_gain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Amp;Focal_Amp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Missense;CNV_Amp;Focal_Amp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Stop_gain;CNV_Del</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNV_Del;Focal_Del</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Stop_gain;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Frameshift;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Missense;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mut_Frameshift;CNV_Loss;Focal_Del</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +591,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,6 +769,30 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -961,7 +1040,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -970,6 +1049,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -6328,7 +6419,7 @@
     </row>
     <row r="45" spans="1:37">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
         <v>0</v>
@@ -6699,7 +6790,7 @@
         <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D50" t="s">
         <v>81</v>
@@ -6708,10 +6799,10 @@
         <v>81</v>
       </c>
       <c r="F50" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="G50" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H50" t="s">
         <v>81</v>
@@ -6720,7 +6811,7 @@
         <v>81</v>
       </c>
       <c r="J50" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="K50" t="s">
         <v>88</v>
@@ -6729,37 +6820,51 @@
         <v>81</v>
       </c>
       <c r="M50" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="N50" t="s">
         <v>81</v>
       </c>
       <c r="O50" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="P50" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="Q50" t="s">
-        <v>81</v>
-      </c>
-      <c r="R50"/>
+        <v>114</v>
+      </c>
+      <c r="R50" t="s">
+        <v>112</v>
+      </c>
       <c r="S50"/>
       <c r="T50"/>
       <c r="U50"/>
       <c r="V50"/>
-      <c r="W50"/>
-      <c r="X50"/>
+      <c r="W50" t="s">
+        <v>112</v>
+      </c>
+      <c r="X50" t="s">
+        <v>112</v>
+      </c>
       <c r="Y50"/>
-      <c r="Z50"/>
+      <c r="Z50" t="s">
+        <v>112</v>
+      </c>
       <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
+      <c r="AB50" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>112</v>
+      </c>
       <c r="AD50"/>
       <c r="AE50"/>
       <c r="AF50"/>
       <c r="AG50"/>
-      <c r="AH50"/>
+      <c r="AH50" t="s">
+        <v>112</v>
+      </c>
       <c r="AI50"/>
       <c r="AJ50"/>
       <c r="AK50"/>
@@ -6837,43 +6942,43 @@
         <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D52"/>
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="H52" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M52"/>
       <c r="N52" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O52"/>
-      <c r="P52" t="s">
-        <v>91</v>
+      <c r="P52" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="Q52"/>
       <c r="R52"/>
-      <c r="S52" t="s">
-        <v>91</v>
+      <c r="S52" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="T52"/>
       <c r="U52"/>
-      <c r="V52" t="s">
-        <v>91</v>
-      </c>
-      <c r="W52" t="s">
-        <v>91</v>
+      <c r="V52" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="X52"/>
       <c r="Y52"/>
@@ -6898,9 +7003,7 @@
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
-      <c r="F53" t="s">
-        <v>91</v>
-      </c>
+      <c r="F53"/>
       <c r="G53"/>
       <c r="H53"/>
       <c r="I53"/>
@@ -6915,11 +7018,9 @@
       <c r="R53"/>
       <c r="S53"/>
       <c r="T53"/>
-      <c r="U53" t="s">
-        <v>91</v>
-      </c>
+      <c r="U53"/>
       <c r="V53" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="W53"/>
       <c r="X53"/>
@@ -6932,7 +7033,7 @@
       <c r="AE53"/>
       <c r="AF53"/>
       <c r="AG53" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AH53"/>
       <c r="AI53"/>
@@ -6955,19 +7056,19 @@
       </c>
       <c r="J54"/>
       <c r="K54" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L54"/>
       <c r="M54" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="N54"/>
       <c r="O54"/>
       <c r="P54" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="Q54" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="R54"/>
       <c r="S54"/>
@@ -6985,7 +7086,7 @@
       <c r="AE54"/>
       <c r="AF54"/>
       <c r="AG54" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AH54"/>
       <c r="AI54"/>
@@ -7001,14 +7102,14 @@
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G55"/>
-      <c r="H55" t="s">
-        <v>94</v>
+      <c r="H55" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J55"/>
       <c r="K55"/>
@@ -7016,26 +7117,23 @@
       <c r="M55"/>
       <c r="N55"/>
       <c r="O55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="P55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="Q55" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="R55"/>
       <c r="S55"/>
       <c r="T55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="U55" t="s">
-        <v>94</v>
-      </c>
-      <c r="V55"/>
-      <c r="W55" t="s">
-        <v>94</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="W55"/>
       <c r="X55"/>
       <c r="Y55"/>
       <c r="Z55"/>
@@ -7046,13 +7144,13 @@
       <c r="AE55"/>
       <c r="AF55"/>
       <c r="AG55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AH55"/>
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -7063,33 +7161,31 @@
         <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56"/>
-      <c r="M56" t="s">
-        <v>94</v>
-      </c>
+      <c r="M56"/>
       <c r="N56"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="R56"/>
       <c r="S56"/>
@@ -7102,14 +7198,14 @@
       <c r="Z56"/>
       <c r="AA56"/>
       <c r="AB56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AC56"/>
       <c r="AD56"/>
       <c r="AE56"/>
       <c r="AF56"/>
       <c r="AG56" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AH56"/>
       <c r="AI56"/>
@@ -7175,52 +7271,52 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58"/>
-      <c r="H58" t="s">
-        <v>91</v>
-      </c>
-      <c r="I58" t="s">
-        <v>91</v>
-      </c>
-      <c r="J58" t="s">
-        <v>91</v>
+      <c r="H58" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="K58" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L58"/>
       <c r="M58" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="N58"/>
       <c r="O58" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="P58" t="s">
         <v>84</v>
       </c>
       <c r="Q58" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="R58" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="S58" t="s">
         <v>85</v>
       </c>
       <c r="T58" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="U58" t="s">
         <v>85</v>
       </c>
       <c r="V58" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="W58" t="s">
         <v>84</v>
       </c>
       <c r="X58" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="Y58" t="s">
         <v>84</v>
@@ -7235,16 +7331,14 @@
         <v>84</v>
       </c>
       <c r="AC58" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AD58"/>
-      <c r="AE58" t="s">
-        <v>91</v>
-      </c>
+      <c r="AE58"/>
       <c r="AF58"/>
       <c r="AG58"/>
       <c r="AH58" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AI58"/>
       <c r="AJ58"/>
@@ -7252,49 +7346,43 @@
     </row>
     <row r="59" spans="1:37">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>94</v>
+        <v>118</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="D59"/>
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="s">
-        <v>94</v>
-      </c>
-      <c r="H59" t="s">
-        <v>94</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="H59"/>
       <c r="I59"/>
       <c r="J59" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="K59"/>
       <c r="L59" t="s">
-        <v>104</v>
-      </c>
-      <c r="M59" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" t="s">
-        <v>94</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="M59"/>
+      <c r="N59"/>
       <c r="O59" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="P59"/>
       <c r="Q59"/>
       <c r="R59" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="S59"/>
       <c r="T59"/>
       <c r="U59" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="V59"/>
       <c r="W59"/>
@@ -7303,56 +7391,56 @@
       </c>
       <c r="Y59"/>
       <c r="Z59" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="AA59"/>
       <c r="AB59"/>
       <c r="AC59"/>
       <c r="AD59"/>
       <c r="AE59" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AF59"/>
       <c r="AG59"/>
       <c r="AH59"/>
       <c r="AI59" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="AJ59"/>
       <c r="AK59"/>
     </row>
     <row r="60" spans="1:37">
       <c r="A60" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" t="s">
-        <v>91</v>
+        <v>102</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60"/>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="J60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="K60"/>
       <c r="L60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M60"/>
       <c r="N60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O60"/>
       <c r="P60"/>
@@ -7366,7 +7454,7 @@
       <c r="X60"/>
       <c r="Y60"/>
       <c r="Z60" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AA60"/>
       <c r="AB60"/>
@@ -7382,46 +7470,42 @@
     </row>
     <row r="61" spans="1:37">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B61"/>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" t="s">
-        <v>94</v>
-      </c>
-      <c r="G61" t="s">
-        <v>94</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F61"/>
+      <c r="G61"/>
       <c r="H61" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61"/>
       <c r="M61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="N61"/>
       <c r="O61"/>
       <c r="P61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="Q61"/>
       <c r="R61"/>
       <c r="S61"/>
       <c r="T61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="U61"/>
       <c r="V61"/>
@@ -7431,14 +7515,14 @@
       <c r="Z61"/>
       <c r="AA61"/>
       <c r="AB61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>
       <c r="AE61"/>
       <c r="AF61"/>
       <c r="AG61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="AH61"/>
       <c r="AI61"/>
@@ -7447,7 +7531,7 @@
     </row>
     <row r="62" spans="1:37">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B62"/>
       <c r="C62"/>
@@ -7492,7 +7576,7 @@
     </row>
     <row r="63" spans="1:37">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B63"/>
       <c r="C63"/>
@@ -7537,7 +7621,7 @@
     </row>
     <row r="64" spans="1:37">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B64"/>
       <c r="C64"/>
@@ -7580,7 +7664,7 @@
     </row>
     <row r="65" spans="1:37">
       <c r="A65" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B65" t="s">
         <v>0</v>
@@ -7693,7 +7777,7 @@
     </row>
     <row r="66" spans="1:37">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B66">
         <v>1</v>
